--- a/upload/previsao_renuncias_novas.xlsx
+++ b/upload/previsao_renuncias_novas.xlsx
@@ -9,11 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="56">
   <si>
     <t>ano</t>
   </si>
@@ -166,19 +169,64 @@
   <si>
     <t>Redução de Base de
 Cálculo</t>
+  </si>
+  <si>
+    <t>DIVINOPOLIS</t>
+  </si>
+  <si>
+    <t>Crédito Presumido(1,2,3 e 4)</t>
+  </si>
+  <si>
+    <t>Indústrias de transformação</t>
+  </si>
+  <si>
+    <t>JUIZ DE FORA</t>
+  </si>
+  <si>
+    <t>Isenção(5)</t>
+  </si>
+  <si>
+    <t>Saúde humana e serviços sociais</t>
+  </si>
+  <si>
+    <t>Redução de Base de Cálculo(5)</t>
+  </si>
+  <si>
+    <t>Água, esgoto, atividades de gestão de resíduos e descontaminação</t>
+  </si>
+  <si>
+    <t>Indústrias de Transformação</t>
+  </si>
+  <si>
+    <t>Eletricidade e Gás</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -198,18 +246,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 15" xfId="2"/>
+    <cellStyle name="Normal 2 4" xfId="1"/>
+    <cellStyle name="Normal 3 4" xfId="3"/>
+    <cellStyle name="Vírgula 15 3" xfId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -487,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -519,67 +574,67 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="F2">
-        <v>26591048.397572469</v>
+        <v>108416.8580261669</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>455099.9423976175</v>
+        <v>408168.32963399985</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F4">
-        <v>3348856.8281873385</v>
+        <v>64182394.855049066</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -588,536 +643,593 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2940044</v>
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>1238023.7295531952</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1260703</v>
+        <v>54</v>
+      </c>
+      <c r="F6">
+        <v>1416996.568033664</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="1">
-        <v>813898</v>
+        <v>55</v>
+      </c>
+      <c r="F7">
+        <v>33908581.842351027</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3086775</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="F8">
+        <v>221623.360051155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2951145</v>
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9">
+        <v>1786.9743456785411</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>387.52211129425706</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="1">
-        <v>987678</v>
+        <v>47</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11">
+        <v>135150.32838324524</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2244486</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+      <c r="F12">
+        <v>1598750.2586201301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>22</v>
+      <c r="D13" t="s">
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="1">
-        <v>381004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+      <c r="F13">
+        <v>2349350.605348059</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>2023</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>2026</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2257009</v>
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>41192.270456695856</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
       </c>
       <c r="F15">
-        <v>17412839</v>
+        <v>9611464.174387766</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
       </c>
       <c r="F16">
-        <v>4172</v>
+        <v>2710826.9017686937</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
       </c>
       <c r="F17">
-        <v>227138561</v>
+        <v>273367.40275657421</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
       </c>
       <c r="F18">
-        <v>79184</v>
+        <v>2569937.8607867579</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
       </c>
       <c r="F19">
-        <v>7336</v>
+        <v>153676.66100313817</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>47</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
       </c>
       <c r="F20">
-        <v>118471991</v>
+        <v>520637.61024809984</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>47</v>
+      </c>
+      <c r="E21" t="s">
+        <v>48</v>
       </c>
       <c r="F21">
-        <v>6244</v>
+        <v>2765490.4202352925</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>32</v>
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>16</v>
       </c>
       <c r="F22">
-        <v>837</v>
+        <v>3348856.8281873385</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>7883838</v>
+        <v>26591048.397572469</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
       </c>
       <c r="F24">
-        <v>3573</v>
+        <v>455099.9423976175</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D25" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
       </c>
       <c r="F25">
-        <v>11419912</v>
+        <v>2940044</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
       </c>
       <c r="F26">
-        <v>5375</v>
+        <v>1260703</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
       </c>
       <c r="F27">
-        <v>28725098</v>
+        <v>813898</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D28" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
       </c>
       <c r="F28">
-        <v>16477</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3086775</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>32</v>
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F29">
-        <v>630</v>
+        <v>2951145</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E30" t="s">
         <v>12</v>
       </c>
       <c r="F30">
-        <v>75289</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>2022</v>
-      </c>
-      <c r="B31" t="s">
-        <v>36</v>
+        <v>2023</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="E31" t="s">
+        <v>25</v>
       </c>
       <c r="F31">
-        <v>16731525</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2257009</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B32" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>30</v>
+        <v>8</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="F32">
-        <v>15183</v>
+        <v>987678</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>28</v>
+        <v>8</v>
+      </c>
+      <c r="E33" t="s">
+        <v>12</v>
       </c>
       <c r="F33">
-        <v>9965643</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2244486</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
-      </c>
-      <c r="D34" t="s">
-        <v>30</v>
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
+        <v>12</v>
       </c>
       <c r="F34">
-        <v>5214</v>
+        <v>381004</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1125,13 +1237,16 @@
         <v>2022</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C35" t="s">
-        <v>10</v>
+        <v>27</v>
+      </c>
+      <c r="D35" t="s">
+        <v>28</v>
       </c>
       <c r="F35">
-        <v>9970857</v>
+        <v>17412839</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1139,19 +1254,16 @@
         <v>2022</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F36">
-        <v>6965124</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1159,19 +1271,16 @@
         <v>2022</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="F37">
-        <v>13828549</v>
+        <v>227138561</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1179,19 +1288,16 @@
         <v>2022</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D38" t="s">
-        <v>39</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F38">
-        <v>84573</v>
+        <v>79184</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,16 +1305,16 @@
         <v>2022</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F39">
-        <v>21957750</v>
+        <v>7336</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1216,16 +1322,16 @@
         <v>2022</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F40">
-        <v>8409</v>
+        <v>2435214</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1233,7 +1339,7 @@
         <v>2022</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C41" t="s">
         <v>27</v>
@@ -1242,7 +1348,7 @@
         <v>28</v>
       </c>
       <c r="F41">
-        <v>6902986</v>
+        <v>118471991</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1250,7 +1356,7 @@
         <v>2022</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C42" t="s">
         <v>29</v>
@@ -1259,7 +1365,7 @@
         <v>30</v>
       </c>
       <c r="F42">
-        <v>6993</v>
+        <v>6244</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1267,7 +1373,7 @@
         <v>2022</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="C43" t="s">
         <v>31</v>
@@ -1276,7 +1382,7 @@
         <v>32</v>
       </c>
       <c r="F43">
-        <v>2530</v>
+        <v>837</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1284,19 +1390,16 @@
         <v>2022</v>
       </c>
       <c r="B44" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="F44">
-        <v>17126615</v>
+        <v>7883838</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1304,16 +1407,16 @@
         <v>2022</v>
       </c>
       <c r="B45" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F45">
-        <v>22066430</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1321,16 +1424,16 @@
         <v>2022</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D46" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F46">
-        <v>10003</v>
+        <v>11419912</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1338,16 +1441,16 @@
         <v>2022</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F47">
-        <v>834</v>
+        <v>5375</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1355,7 +1458,7 @@
         <v>2022</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
         <v>27</v>
@@ -1364,7 +1467,7 @@
         <v>28</v>
       </c>
       <c r="F48">
-        <v>26812113</v>
+        <v>28725098</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1372,7 +1475,7 @@
         <v>2022</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C49" t="s">
         <v>29</v>
@@ -1381,7 +1484,7 @@
         <v>30</v>
       </c>
       <c r="F49">
-        <v>12327</v>
+        <v>16477</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,7 +1492,7 @@
         <v>2022</v>
       </c>
       <c r="B50" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="C50" t="s">
         <v>31</v>
@@ -1398,7 +1501,7 @@
         <v>32</v>
       </c>
       <c r="F50">
-        <v>3350</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1406,16 +1509,19 @@
         <v>2022</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C51" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="E51" t="s">
+        <v>12</v>
       </c>
       <c r="F51">
-        <v>33326953</v>
+        <v>75289</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1423,16 +1529,16 @@
         <v>2022</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D52" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F52">
-        <v>12110</v>
+        <v>16731525</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1440,16 +1546,16 @@
         <v>2022</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C53" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F53">
-        <v>2962</v>
+        <v>15183</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1457,7 +1563,7 @@
         <v>2022</v>
       </c>
       <c r="B54" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -1466,52 +1572,43 @@
         <v>28</v>
       </c>
       <c r="F54">
-        <v>2435214</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>9965643</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E55" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="1">
-        <v>5399048</v>
+        <v>29</v>
+      </c>
+      <c r="D55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>5214</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B56" t="s">
         <v>38</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" t="s">
-        <v>37</v>
-      </c>
-      <c r="E56" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="1">
-        <v>793383</v>
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>9970857</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B57" t="s">
         <v>6</v>
@@ -1525,16 +1622,16 @@
       <c r="E57" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="1">
-        <v>1164023</v>
+      <c r="F57">
+        <v>6965124</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C58" t="s">
         <v>7</v>
@@ -1543,53 +1640,416 @@
         <v>37</v>
       </c>
       <c r="E58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="1">
-        <v>101140</v>
+        <v>9</v>
+      </c>
+      <c r="F58">
+        <v>13828549</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C59" t="s">
         <v>7</v>
       </c>
       <c r="D59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E59" t="s">
         <v>12</v>
       </c>
-      <c r="F59" s="1">
-        <v>1479980</v>
+      <c r="F59">
+        <v>84573</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
+        <v>2022</v>
+      </c>
+      <c r="B60" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>40</v>
+      </c>
+      <c r="F60">
+        <v>21957750</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2022</v>
+      </c>
+      <c r="B61" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" t="s">
+        <v>30</v>
+      </c>
+      <c r="F61">
+        <v>8409</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2022</v>
+      </c>
+      <c r="B62" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62">
+        <v>6902986</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2022</v>
+      </c>
+      <c r="B63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63">
+        <v>6993</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2022</v>
+      </c>
+      <c r="B64" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" t="s">
+        <v>32</v>
+      </c>
+      <c r="F64">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2022</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65">
+        <v>17126615</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2022</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66">
+        <v>22066430</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2022</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
+        <v>30</v>
+      </c>
+      <c r="F67">
+        <v>10003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2022</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>42</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="F68">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2022</v>
+      </c>
+      <c r="B69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69">
+        <v>26812113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2022</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70">
+        <v>12327</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2022</v>
+      </c>
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>31</v>
+      </c>
+      <c r="D71" t="s">
+        <v>32</v>
+      </c>
+      <c r="F71">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2022</v>
+      </c>
+      <c r="B72" t="s">
+        <v>43</v>
+      </c>
+      <c r="C72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72">
+        <v>33326953</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2022</v>
+      </c>
+      <c r="B73" t="s">
+        <v>43</v>
+      </c>
+      <c r="C73" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73">
+        <v>12110</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2022</v>
+      </c>
+      <c r="B74" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" t="s">
+        <v>31</v>
+      </c>
+      <c r="D74" t="s">
+        <v>32</v>
+      </c>
+      <c r="F74">
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>2021</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75">
+        <v>5399048</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2021</v>
+      </c>
+      <c r="B76" t="s">
+        <v>38</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76">
+        <v>793383</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2021</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77">
+        <v>1164023</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2021</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>7</v>
+      </c>
+      <c r="D78" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78">
+        <v>101140</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2021</v>
+      </c>
+      <c r="B79" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79">
+        <v>1479980</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2021</v>
+      </c>
+      <c r="B80" t="s">
         <v>43</v>
       </c>
-      <c r="C60" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" t="s">
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
         <v>37</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E80" t="s">
         <v>12</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F80">
         <v>156163</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1">
+    <sortState ref="A2:F80">
+      <sortCondition descending="1" ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/upload/previsao_renuncias_novas.xlsx
+++ b/upload/previsao_renuncias_novas.xlsx
@@ -9,13 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17925" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$G$80</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="63">
   <si>
     <t>ano</t>
   </si>
@@ -199,6 +199,27 @@
   </si>
   <si>
     <t>Eletricidade e Gás</t>
+  </si>
+  <si>
+    <t>norma_autorizadora</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 25.440, de 06/08/2025</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.945, de 02/08/2024</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.404, de 02/08/2023</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.218, 15/07/2022</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 24.831, 28/07/2021</t>
+  </si>
+  <si>
+    <t>inciso IX do artigo 7º da Lei nº 23.685, 07/08/2020</t>
   </si>
 </sst>
 </file>
@@ -542,17 +563,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="56.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.140625" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -569,10 +591,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2026</v>
       </c>
@@ -588,11 +613,14 @@
       <c r="E2" t="s">
         <v>53</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2">
         <v>108416.8580261669</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2026</v>
       </c>
@@ -608,11 +636,14 @@
       <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3">
         <v>408168.32963399985</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2026</v>
       </c>
@@ -628,11 +659,14 @@
       <c r="E4" t="s">
         <v>54</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G4">
         <v>64182394.855049066</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2026</v>
       </c>
@@ -648,11 +682,14 @@
       <c r="E5" t="s">
         <v>51</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5">
         <v>1238023.7295531952</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -668,11 +705,14 @@
       <c r="E6" t="s">
         <v>54</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6">
         <v>1416996.568033664</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2026</v>
       </c>
@@ -688,11 +728,14 @@
       <c r="E7" t="s">
         <v>55</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7">
         <v>33908581.842351027</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2026</v>
       </c>
@@ -708,11 +751,14 @@
       <c r="E8" t="s">
         <v>48</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8">
         <v>221623.360051155</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2026</v>
       </c>
@@ -728,11 +774,14 @@
       <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9">
         <v>1786.9743456785411</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2026</v>
       </c>
@@ -748,11 +797,14 @@
       <c r="E10" t="s">
         <v>9</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10">
         <v>387.52211129425706</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2026</v>
       </c>
@@ -768,11 +820,14 @@
       <c r="E11" t="s">
         <v>48</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11">
         <v>135150.32838324524</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2026</v>
       </c>
@@ -788,11 +843,14 @@
       <c r="E12" t="s">
         <v>51</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12">
         <v>1598750.2586201301</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2026</v>
       </c>
@@ -808,11 +866,14 @@
       <c r="E13" t="s">
         <v>48</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13">
         <v>2349350.605348059</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2026</v>
       </c>
@@ -828,11 +889,14 @@
       <c r="E14" t="s">
         <v>48</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14">
         <v>41192.270456695856</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2026</v>
       </c>
@@ -848,11 +912,14 @@
       <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15">
         <v>9611464.174387766</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2026</v>
       </c>
@@ -868,11 +935,14 @@
       <c r="E16" t="s">
         <v>48</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
         <v>2710826.9017686937</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2026</v>
       </c>
@@ -888,11 +958,14 @@
       <c r="E17" t="s">
         <v>9</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
         <v>273367.40275657421</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>2026</v>
       </c>
@@ -908,11 +981,14 @@
       <c r="E18" t="s">
         <v>48</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
         <v>2569937.8607867579</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>2026</v>
       </c>
@@ -928,11 +1004,14 @@
       <c r="E19" t="s">
         <v>48</v>
       </c>
-      <c r="F19">
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
         <v>153676.66100313817</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2026</v>
       </c>
@@ -948,11 +1027,14 @@
       <c r="E20" t="s">
         <v>9</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20">
         <v>520637.61024809984</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2026</v>
       </c>
@@ -968,11 +1050,14 @@
       <c r="E21" t="s">
         <v>48</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21">
         <v>2765490.4202352925</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>2025</v>
       </c>
@@ -988,11 +1073,14 @@
       <c r="E22" t="s">
         <v>16</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22">
         <v>3348856.8281873385</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>2025</v>
       </c>
@@ -1008,11 +1096,14 @@
       <c r="E23" t="s">
         <v>9</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23">
         <v>26591048.397572469</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>2025</v>
       </c>
@@ -1028,11 +1119,14 @@
       <c r="E24" t="s">
         <v>12</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="s">
+        <v>58</v>
+      </c>
+      <c r="G24">
         <v>455099.9423976175</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>2024</v>
       </c>
@@ -1048,11 +1142,14 @@
       <c r="E25" t="s">
         <v>12</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25">
         <v>2940044</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2024</v>
       </c>
@@ -1068,11 +1165,14 @@
       <c r="E26" t="s">
         <v>12</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26">
         <v>1260703</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -1088,11 +1188,14 @@
       <c r="E27" t="s">
         <v>9</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27">
         <v>813898</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>2024</v>
       </c>
@@ -1108,11 +1211,14 @@
       <c r="E28" t="s">
         <v>12</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28">
         <v>3086775</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>2023</v>
       </c>
@@ -1128,11 +1234,14 @@
       <c r="E29" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29">
         <v>2951145</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2023</v>
       </c>
@@ -1148,11 +1257,14 @@
       <c r="E30" t="s">
         <v>12</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30">
         <v>1032</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2023</v>
       </c>
@@ -1168,11 +1280,14 @@
       <c r="E31" t="s">
         <v>25</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31">
         <v>2257009</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2023</v>
       </c>
@@ -1188,11 +1303,14 @@
       <c r="E32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G32">
         <v>987678</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2023</v>
       </c>
@@ -1208,11 +1326,14 @@
       <c r="E33" t="s">
         <v>12</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G33">
         <v>2244486</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2023</v>
       </c>
@@ -1228,11 +1349,14 @@
       <c r="E34" t="s">
         <v>12</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34">
         <v>381004</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2022</v>
       </c>
@@ -1245,11 +1369,14 @@
       <c r="D35" t="s">
         <v>28</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G35">
         <v>17412839</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2022</v>
       </c>
@@ -1262,11 +1389,14 @@
       <c r="D36" t="s">
         <v>30</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G36">
         <v>4172</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2022</v>
       </c>
@@ -1279,11 +1409,14 @@
       <c r="D37" t="s">
         <v>28</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37">
         <v>227138561</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2022</v>
       </c>
@@ -1296,11 +1429,14 @@
       <c r="D38" t="s">
         <v>30</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38">
         <v>79184</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2022</v>
       </c>
@@ -1313,11 +1449,14 @@
       <c r="D39" t="s">
         <v>32</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39">
         <v>7336</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2022</v>
       </c>
@@ -1330,11 +1469,14 @@
       <c r="D40" t="s">
         <v>28</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G40">
         <v>2435214</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2022</v>
       </c>
@@ -1347,11 +1489,14 @@
       <c r="D41" t="s">
         <v>28</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G41">
         <v>118471991</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2022</v>
       </c>
@@ -1364,11 +1509,14 @@
       <c r="D42" t="s">
         <v>30</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G42">
         <v>6244</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2022</v>
       </c>
@@ -1381,11 +1529,14 @@
       <c r="D43" t="s">
         <v>32</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G43">
         <v>837</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2022</v>
       </c>
@@ -1398,11 +1549,14 @@
       <c r="D44" t="s">
         <v>28</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G44">
         <v>7883838</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2022</v>
       </c>
@@ -1415,11 +1569,14 @@
       <c r="D45" t="s">
         <v>30</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45">
         <v>3573</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2022</v>
       </c>
@@ -1432,11 +1589,14 @@
       <c r="D46" t="s">
         <v>28</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46">
         <v>11419912</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2022</v>
       </c>
@@ -1449,11 +1609,14 @@
       <c r="D47" t="s">
         <v>30</v>
       </c>
-      <c r="F47">
+      <c r="F47" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47">
         <v>5375</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2022</v>
       </c>
@@ -1466,11 +1629,14 @@
       <c r="D48" t="s">
         <v>28</v>
       </c>
-      <c r="F48">
+      <c r="F48" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G48">
         <v>28725098</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2022</v>
       </c>
@@ -1483,11 +1649,14 @@
       <c r="D49" t="s">
         <v>30</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G49">
         <v>16477</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2022</v>
       </c>
@@ -1500,11 +1669,14 @@
       <c r="D50" t="s">
         <v>32</v>
       </c>
-      <c r="F50">
+      <c r="F50" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G50">
         <v>630</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2022</v>
       </c>
@@ -1520,11 +1692,14 @@
       <c r="E51" t="s">
         <v>12</v>
       </c>
-      <c r="F51">
+      <c r="F51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G51">
         <v>75289</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2022</v>
       </c>
@@ -1537,11 +1712,14 @@
       <c r="D52" t="s">
         <v>28</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G52">
         <v>16731525</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2022</v>
       </c>
@@ -1554,11 +1732,14 @@
       <c r="D53" t="s">
         <v>30</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G53">
         <v>15183</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2022</v>
       </c>
@@ -1571,11 +1752,14 @@
       <c r="D54" t="s">
         <v>28</v>
       </c>
-      <c r="F54">
+      <c r="F54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G54">
         <v>9965643</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2022</v>
       </c>
@@ -1588,11 +1772,14 @@
       <c r="D55" t="s">
         <v>30</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55">
         <v>5214</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2022</v>
       </c>
@@ -1602,11 +1789,14 @@
       <c r="C56" t="s">
         <v>10</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G56">
         <v>9970857</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2022</v>
       </c>
@@ -1622,11 +1812,14 @@
       <c r="E57" t="s">
         <v>12</v>
       </c>
-      <c r="F57">
+      <c r="F57" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G57">
         <v>6965124</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>2022</v>
       </c>
@@ -1642,11 +1835,14 @@
       <c r="E58" t="s">
         <v>9</v>
       </c>
-      <c r="F58">
+      <c r="F58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G58">
         <v>13828549</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>2022</v>
       </c>
@@ -1662,11 +1858,14 @@
       <c r="E59" t="s">
         <v>12</v>
       </c>
-      <c r="F59">
+      <c r="F59" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G59">
         <v>84573</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>2022</v>
       </c>
@@ -1679,11 +1878,14 @@
       <c r="D60" t="s">
         <v>40</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G60">
         <v>21957750</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>2022</v>
       </c>
@@ -1696,11 +1898,14 @@
       <c r="D61" t="s">
         <v>30</v>
       </c>
-      <c r="F61">
+      <c r="F61" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G61">
         <v>8409</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>2022</v>
       </c>
@@ -1713,11 +1918,14 @@
       <c r="D62" t="s">
         <v>28</v>
       </c>
-      <c r="F62">
+      <c r="F62" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62">
         <v>6902986</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>2022</v>
       </c>
@@ -1730,11 +1938,14 @@
       <c r="D63" t="s">
         <v>30</v>
       </c>
-      <c r="F63">
+      <c r="F63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63">
         <v>6993</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>2022</v>
       </c>
@@ -1747,11 +1958,14 @@
       <c r="D64" t="s">
         <v>32</v>
       </c>
-      <c r="F64">
+      <c r="F64" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G64">
         <v>2530</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>2022</v>
       </c>
@@ -1767,11 +1981,14 @@
       <c r="E65" t="s">
         <v>12</v>
       </c>
-      <c r="F65">
+      <c r="F65" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65">
         <v>17126615</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>2022</v>
       </c>
@@ -1784,11 +2001,14 @@
       <c r="D66" t="s">
         <v>28</v>
       </c>
-      <c r="F66">
+      <c r="F66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66">
         <v>22066430</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>2022</v>
       </c>
@@ -1801,11 +2021,14 @@
       <c r="D67" t="s">
         <v>30</v>
       </c>
-      <c r="F67">
+      <c r="F67" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G67">
         <v>10003</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>2022</v>
       </c>
@@ -1818,11 +2041,14 @@
       <c r="D68" t="s">
         <v>32</v>
       </c>
-      <c r="F68">
+      <c r="F68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G68">
         <v>834</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>2022</v>
       </c>
@@ -1835,11 +2061,14 @@
       <c r="D69" t="s">
         <v>28</v>
       </c>
-      <c r="F69">
+      <c r="F69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G69">
         <v>26812113</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>2022</v>
       </c>
@@ -1852,11 +2081,14 @@
       <c r="D70" t="s">
         <v>30</v>
       </c>
-      <c r="F70">
+      <c r="F70" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G70">
         <v>12327</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>2022</v>
       </c>
@@ -1869,11 +2101,14 @@
       <c r="D71" t="s">
         <v>32</v>
       </c>
-      <c r="F71">
+      <c r="F71" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G71">
         <v>3350</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>2022</v>
       </c>
@@ -1886,11 +2121,14 @@
       <c r="D72" t="s">
         <v>28</v>
       </c>
-      <c r="F72">
+      <c r="F72" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G72">
         <v>33326953</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>2022</v>
       </c>
@@ -1903,11 +2141,14 @@
       <c r="D73" t="s">
         <v>30</v>
       </c>
-      <c r="F73">
+      <c r="F73" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G73">
         <v>12110</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>2022</v>
       </c>
@@ -1920,11 +2161,14 @@
       <c r="D74" t="s">
         <v>32</v>
       </c>
-      <c r="F74">
+      <c r="F74" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G74">
         <v>2962</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>2021</v>
       </c>
@@ -1940,11 +2184,14 @@
       <c r="E75" t="s">
         <v>12</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G75">
         <v>5399048</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>2021</v>
       </c>
@@ -1960,11 +2207,14 @@
       <c r="E76" t="s">
         <v>12</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G76">
         <v>793383</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>2021</v>
       </c>
@@ -1980,11 +2230,14 @@
       <c r="E77" t="s">
         <v>12</v>
       </c>
-      <c r="F77">
+      <c r="F77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G77">
         <v>1164023</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>2021</v>
       </c>
@@ -2000,11 +2253,14 @@
       <c r="E78" t="s">
         <v>12</v>
       </c>
-      <c r="F78">
+      <c r="F78" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G78">
         <v>101140</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>2021</v>
       </c>
@@ -2020,11 +2276,14 @@
       <c r="E79" t="s">
         <v>12</v>
       </c>
-      <c r="F79">
+      <c r="F79" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G79">
         <v>1479980</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>2021</v>
       </c>
@@ -2040,12 +2299,15 @@
       <c r="E80" t="s">
         <v>12</v>
       </c>
-      <c r="F80">
+      <c r="F80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G80">
         <v>156163</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1">
+  <autoFilter ref="A1:G80">
     <sortState ref="A2:F80">
       <sortCondition descending="1" ref="A1"/>
     </sortState>
